--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,6 +1372,1083 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133600670</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544490</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6692565</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133602070</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>544892</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6692559</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133602312</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>544920</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6692568</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133601323</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>544803</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6692605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133602027</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544909</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6692587</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133602565</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>544945</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6692558</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133602389</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>544937</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6692572</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133602525</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>544946</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6692565</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133603452</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>544887</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6692545</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133601878</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93242</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>544909</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6692587</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133602643</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104642</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>544958</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6692555</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B16" t="n">
-        <v>104642</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R16" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>104642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R17" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>104642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R16" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>104642</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R17" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B11" t="n">
-        <v>104642</v>
+        <v>101338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R11" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B12" t="n">
-        <v>101338</v>
+        <v>104642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R12" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B14" t="n">
         <v>104642</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R14" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B15" t="n">
         <v>104642</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R15" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B16" t="n">
-        <v>104642</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R16" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>104642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R17" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>101338</v>
+        <v>104644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R11" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>104642</v>
+        <v>101340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R12" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B14" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R14" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B15" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R15" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>104644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R16" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>104642</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R17" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2255,7 +2255,7 @@
         <v>133601878</v>
       </c>
       <c r="B18" t="n">
-        <v>93242</v>
+        <v>93244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133602643</v>
       </c>
       <c r="B19" t="n">
-        <v>104642</v>
+        <v>104644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B16" t="n">
-        <v>104644</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R16" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>104644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R17" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B11" t="n">
-        <v>104644</v>
+        <v>101348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R11" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B12" t="n">
-        <v>101340</v>
+        <v>104652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R12" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>133602565</v>
       </c>
       <c r="B14" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>133602389</v>
       </c>
       <c r="B15" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>133603452</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>133602525</v>
       </c>
       <c r="B17" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>133601878</v>
       </c>
       <c r="B18" t="n">
-        <v>93244</v>
+        <v>93252</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133602643</v>
       </c>
       <c r="B19" t="n">
-        <v>104644</v>
+        <v>104652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>101348</v>
+        <v>104652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R11" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>104652</v>
+        <v>101348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R12" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B11" t="n">
-        <v>104652</v>
+        <v>101348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R11" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B12" t="n">
-        <v>101348</v>
+        <v>104652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R12" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>133602070</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>101348</v>
+        <v>101376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B14" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R14" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B15" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R15" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2058,32 +2058,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133603452</v>
+        <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>104680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544887</v>
+        <v>544946</v>
       </c>
       <c r="R16" t="n">
-        <v>6692545</v>
+        <v>6692565</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133602525</v>
+        <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>104652</v>
+        <v>91947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R17" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2255,7 +2255,7 @@
         <v>133601878</v>
       </c>
       <c r="B18" t="n">
-        <v>93252</v>
+        <v>93280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133602643</v>
       </c>
       <c r="B19" t="n">
-        <v>104652</v>
+        <v>104680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B14" t="n">
         <v>104680</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R14" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B15" t="n">
         <v>104680</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R15" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>133602070</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>101376</v>
+        <v>101386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>133602565</v>
       </c>
       <c r="B14" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>133602389</v>
       </c>
       <c r="B15" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>133601878</v>
       </c>
       <c r="B18" t="n">
-        <v>93280</v>
+        <v>93290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>133602643</v>
       </c>
       <c r="B19" t="n">
-        <v>104680</v>
+        <v>104690</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B11" t="n">
-        <v>104690</v>
+        <v>101386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R11" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B12" t="n">
-        <v>101386</v>
+        <v>104690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R12" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B14" t="n">
         <v>104690</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R14" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B15" t="n">
         <v>104690</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R15" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133601323</v>
+        <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>101386</v>
+        <v>104690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544803</v>
+        <v>544920</v>
       </c>
       <c r="R11" t="n">
-        <v>6692605</v>
+        <v>6692568</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133602312</v>
+        <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>104690</v>
+        <v>101386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544920</v>
+        <v>544803</v>
       </c>
       <c r="R12" t="n">
-        <v>6692568</v>
+        <v>6692605</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133601878</v>
+        <v>133602643</v>
       </c>
       <c r="B18" t="n">
-        <v>93290</v>
+        <v>104690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544909</v>
+        <v>544958</v>
       </c>
       <c r="R18" t="n">
-        <v>6692587</v>
+        <v>6692555</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133602643</v>
+        <v>133601878</v>
       </c>
       <c r="B19" t="n">
-        <v>104690</v>
+        <v>93290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544958</v>
+        <v>544909</v>
       </c>
       <c r="R19" t="n">
-        <v>6692555</v>
+        <v>6692587</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>101386</v>
+        <v>101388</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B14" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R14" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B15" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R15" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2061,7 +2061,7 @@
         <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>104690</v>
+        <v>104692</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133602643</v>
+        <v>133601878</v>
       </c>
       <c r="B18" t="n">
-        <v>104690</v>
+        <v>93292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544958</v>
+        <v>544909</v>
       </c>
       <c r="R18" t="n">
-        <v>6692555</v>
+        <v>6692587</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2323,6 +2323,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133601878</v>
+        <v>133602643</v>
       </c>
       <c r="B19" t="n">
-        <v>93290</v>
+        <v>104692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544909</v>
+        <v>544958</v>
       </c>
       <c r="R19" t="n">
-        <v>6692587</v>
+        <v>6692555</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2420,11 +2425,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1864,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B14" t="n">
         <v>104693</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R14" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B15" t="n">
         <v>104693</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R15" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -1377,7 +1377,7 @@
         <v>133600670</v>
       </c>
       <c r="B9" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>133602312</v>
       </c>
       <c r="B11" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>133601323</v>
       </c>
       <c r="B12" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>133602027</v>
       </c>
       <c r="B13" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602389</v>
+        <v>133602565</v>
       </c>
       <c r="B14" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544937</v>
+        <v>544945</v>
       </c>
       <c r="R14" t="n">
-        <v>6692572</v>
+        <v>6692558</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602565</v>
+        <v>133602389</v>
       </c>
       <c r="B15" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544945</v>
+        <v>544937</v>
       </c>
       <c r="R15" t="n">
-        <v>6692558</v>
+        <v>6692572</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2061,7 +2061,7 @@
         <v>133602525</v>
       </c>
       <c r="B16" t="n">
-        <v>104693</v>
+        <v>104700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>133603452</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133601878</v>
+        <v>133602643</v>
       </c>
       <c r="B18" t="n">
-        <v>93293</v>
+        <v>104700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544909</v>
+        <v>544958</v>
       </c>
       <c r="R18" t="n">
-        <v>6692587</v>
+        <v>6692555</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2323,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133602643</v>
+        <v>133601878</v>
       </c>
       <c r="B19" t="n">
-        <v>104693</v>
+        <v>93300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544958</v>
+        <v>544909</v>
       </c>
       <c r="R19" t="n">
-        <v>6692555</v>
+        <v>6692587</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2425,6 +2420,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12812-2026 artfynd.xlsx
+++ b/artfynd/A 12812-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132061522</v>
+        <v>133603452</v>
       </c>
       <c r="B2" t="n">
-        <v>101327</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544864</v>
+        <v>544887</v>
       </c>
       <c r="R2" t="n">
-        <v>6692539</v>
+        <v>6692545</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132061089</v>
+        <v>132060397</v>
       </c>
       <c r="B3" t="n">
-        <v>101327</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544818</v>
+        <v>544425</v>
       </c>
       <c r="R3" t="n">
-        <v>6692614</v>
+        <v>6692496</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132061139</v>
+        <v>132060847</v>
       </c>
       <c r="B4" t="n">
-        <v>93234</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544821</v>
+        <v>544699</v>
       </c>
       <c r="R4" t="n">
-        <v>6692613</v>
+        <v>6692624</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132061658</v>
+        <v>132061113</v>
       </c>
       <c r="B5" t="n">
-        <v>93234</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544585</v>
+        <v>544814</v>
       </c>
       <c r="R5" t="n">
-        <v>6692450</v>
+        <v>6692615</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132060836</v>
+        <v>132061423</v>
       </c>
       <c r="B6" t="n">
-        <v>101327</v>
+        <v>96410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,39 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gropbo, Gropbo, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544699</v>
+        <v>544894</v>
       </c>
       <c r="R6" t="n">
-        <v>6692624</v>
+        <v>6692527</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1175,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132061102</v>
+        <v>132061527</v>
       </c>
       <c r="B7" t="n">
-        <v>104629</v>
+        <v>96410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544814</v>
+        <v>544864</v>
       </c>
       <c r="R7" t="n">
-        <v>6692615</v>
+        <v>6692539</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1272,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132061628</v>
+        <v>133601450</v>
       </c>
       <c r="B8" t="n">
-        <v>93234</v>
+        <v>96410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544585</v>
+        <v>544898</v>
       </c>
       <c r="R8" t="n">
-        <v>6692543</v>
+        <v>6692610</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1332,22 +1317,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Säter</t>
+          <t>Stora Skedvi</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133600670</v>
+        <v>132061139</v>
       </c>
       <c r="B9" t="n">
-        <v>104700</v>
+        <v>93307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544490</v>
+        <v>544821</v>
       </c>
       <c r="R9" t="n">
-        <v>6692565</v>
+        <v>6692613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,12 +1419,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133602070</v>
+        <v>132061438</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>93307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gropbo, Gropbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544892</v>
+        <v>544906</v>
       </c>
       <c r="R10" t="n">
-        <v>6692559</v>
+        <v>6692526</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1541,12 +1521,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133602312</v>
+        <v>132061628</v>
       </c>
       <c r="B11" t="n">
-        <v>104700</v>
+        <v>93307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544920</v>
+        <v>544585</v>
       </c>
       <c r="R11" t="n">
-        <v>6692568</v>
+        <v>6692543</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1638,12 +1623,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133601323</v>
+        <v>132061658</v>
       </c>
       <c r="B12" t="n">
-        <v>101396</v>
+        <v>93307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544803</v>
+        <v>544585</v>
       </c>
       <c r="R12" t="n">
-        <v>6692605</v>
+        <v>6692450</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1735,12 +1725,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,32 +1762,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133602027</v>
+        <v>133601878</v>
       </c>
       <c r="B13" t="n">
-        <v>104700</v>
+        <v>93307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133602565</v>
+        <v>133601467</v>
       </c>
       <c r="B14" t="n">
-        <v>104700</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1875,34 +1875,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gropbo, Gropbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544945</v>
+        <v>544911</v>
       </c>
       <c r="R14" t="n">
-        <v>6692558</v>
+        <v>6692605</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1924,7 +1929,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Säter</t>
+          <t>Stora Skedvi</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1961,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133602389</v>
+        <v>133602070</v>
       </c>
       <c r="B15" t="n">
-        <v>104700</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1972,34 +1977,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gropbo, Gropbo, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544937</v>
+        <v>544892</v>
       </c>
       <c r="R15" t="n">
-        <v>6692572</v>
+        <v>6692559</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2058,27 +2068,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133602525</v>
+        <v>133603685</v>
       </c>
       <c r="B16" t="n">
-        <v>104700</v>
+        <v>101974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>220075</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2093,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544946</v>
+        <v>544887</v>
       </c>
       <c r="R16" t="n">
-        <v>6692565</v>
+        <v>6692545</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2155,32 +2165,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133603452</v>
+        <v>132061102</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>104707</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544887</v>
+        <v>544814</v>
       </c>
       <c r="R17" t="n">
-        <v>6692545</v>
+        <v>6692615</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2220,12 +2230,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133602643</v>
+        <v>133600670</v>
       </c>
       <c r="B18" t="n">
-        <v>104700</v>
+        <v>104707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544958</v>
+        <v>544490</v>
       </c>
       <c r="R18" t="n">
-        <v>6692555</v>
+        <v>6692565</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2349,10 +2359,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133601878</v>
+        <v>133602027</v>
       </c>
       <c r="B19" t="n">
-        <v>93300</v>
+        <v>104707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2370,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2422,11 +2432,6 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2448,6 +2453,1762 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133602312</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>544920</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6692568</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133602389</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>544937</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6692572</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133602483</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>544943</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6692573</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133602525</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>544946</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6692565</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133602565</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>544945</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6692558</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133602643</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>544958</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6692555</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132060836</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>544699</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6692624</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132060899</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>544741</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6692642</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132060961</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>544781</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6692640</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132061089</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>544818</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6692614</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132061429</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>544906</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6692526</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132061522</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>544864</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6692539</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133601323</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>544803</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6692605</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133602509</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>544941</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6692572</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133601713</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>544902</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6692609</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133602257</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>544920</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6692568</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132060641</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>544425</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6692496</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132060933</v>
+      </c>
+      <c r="B37" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gropbo, Gropbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>544741</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6692642</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Med bohål.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
